--- a/20250519_SA_ternary/output/20250519_SA_ternary_site_pairs.xlsx
+++ b/20250519_SA_ternary/output/20250519_SA_ternary_site_pairs.xlsx
@@ -962,7 +962,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1233938.cif</t>
+          <t>1803512.cif</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -977,7 +977,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1803512.cif</t>
+          <t>1233938.cif</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1826,7 +1826,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1803512.cif</t>
+          <t>1233938.cif</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1841,7 +1841,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233938.cif</t>
+          <t>1803512.cif</t>
         </is>
       </c>
       <c r="B18" t="n">
